--- a/quests/GuildWars_Quest_Tracker.xlsx
+++ b/quests/GuildWars_Quest_Tracker.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Pre-Searing Quests" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pre-Searing Quests" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pre-Searing Quests'!$A$1:$I$68</definedName>
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3206,6 +3206,181 @@
       </c>
       <c r="I68" s="4" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Getting Started in Guild Wars</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Town Crier</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Ascalon City</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Reforged Mode</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>500 XP, 100g</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>A Bastion In the North</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ben Wolfson</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Lakeside County</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Reforged Mode, Across the Wall</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>250 XP, 100g</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Long Thought Forgotten</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Adept Mullenix</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Piken Square (pre)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>A Bastion In the North</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>250 XP, 100g, Elemental Crystal Shard</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Charr in the Tunnels</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Lieutenant Greywind</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Piken Square (pre)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Long Thought Forgotten</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>250 XP, 100g</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>The Scourge Beneath</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Devona</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Piken Square (pre)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Charr in the Tunnels</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>250 XP, 100g, Devona (Hero)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
